--- a/Case_Study/Sample_use_case_setup.xlsx
+++ b/Case_Study/Sample_use_case_setup.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yli6/Desktop/NREL/Project/HYPSTAT/HYPSTAT_github/Case_Study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jbrauch\Desktop\HYPSTAT open sourcing\HYPSTAT\Case_Study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEE1067-9716-3446-A7B6-6A224388B13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6572167F-6DB3-4143-ADA7-C1D4743DA91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19060" xr2:uid="{8240C5C8-55BB-784E-92A0-705DB0403669}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8240C5C8-55BB-784E-92A0-705DB0403669}"/>
   </bookViews>
   <sheets>
     <sheet name="Zone" sheetId="1" r:id="rId1"/>
-    <sheet name="Technology" sheetId="2" r:id="rId2"/>
-    <sheet name="Cost reference" sheetId="3" r:id="rId3"/>
-    <sheet name="Financial Inputs" sheetId="4" r:id="rId4"/>
+    <sheet name="Demands" sheetId="5" r:id="rId2"/>
+    <sheet name="Technology" sheetId="2" r:id="rId3"/>
+    <sheet name="Cost reference" sheetId="3" r:id="rId4"/>
+    <sheet name="Financial Inputs" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="72">
   <si>
     <t>Node</t>
   </si>
@@ -62,9 +63,6 @@
     <t>Demand</t>
   </si>
   <si>
-    <t>Supply</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
@@ -110,12 +108,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>Pipeline allowed</t>
-  </si>
-  <si>
-    <t>Truck Allowed</t>
-  </si>
-  <si>
     <t>Cost Reference</t>
   </si>
   <si>
@@ -146,9 +138,6 @@
     <t>Pipelines</t>
   </si>
   <si>
-    <t>Compressors</t>
-  </si>
-  <si>
     <t>Discount_Rate</t>
   </si>
   <si>
@@ -161,27 +150,15 @@
     <t>H2 Delivery</t>
   </si>
   <si>
-    <t>Compressor</t>
-  </si>
-  <si>
     <t>All years</t>
   </si>
   <si>
     <t>NO</t>
   </si>
   <si>
-    <t>Tank Allowed</t>
-  </si>
-  <si>
-    <t>Cavern Allowed</t>
-  </si>
-  <si>
     <t>NREL Cambium (Mid-case) for US national in hourly resolution (total_cost_enduse)</t>
   </si>
   <si>
-    <t>Solid Oxide Electrolyzer</t>
-  </si>
-  <si>
     <t>Wind &amp; Solar</t>
   </si>
   <si>
@@ -192,13 +169,100 @@
   </si>
   <si>
     <t>5 node</t>
+  </si>
+  <si>
+    <t>Geologic Storage</t>
+  </si>
+  <si>
+    <t>Tank Storage</t>
+  </si>
+  <si>
+    <t>LBW</t>
+  </si>
+  <si>
+    <t>Geologic</t>
+  </si>
+  <si>
+    <t>LCOE from H2@Scale</t>
+  </si>
+  <si>
+    <t>OSW</t>
+  </si>
+  <si>
+    <t>Descriptor</t>
+  </si>
+  <si>
+    <t>Coastal</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Inland</t>
+  </si>
+  <si>
+    <t>Connection point</t>
+  </si>
+  <si>
+    <t>Suburb</t>
+  </si>
+  <si>
+    <t>Industrial site</t>
+  </si>
+  <si>
+    <t>Demand types</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Relatively large, flat</t>
+  </si>
+  <si>
+    <t>Medium, port (relatively flat)</t>
+  </si>
+  <si>
+    <t>Rough magnitude (annual kT)</t>
+  </si>
+  <si>
+    <t>Large, summer peak for power gen</t>
+  </si>
+  <si>
+    <t>Medium, winter peak for heating, baseline demand for fleet vehicles</t>
+  </si>
+  <si>
+    <t>Small demand, for HD FCEVs (relatively flat)</t>
+  </si>
+  <si>
+    <t>YES (20 kT)</t>
+  </si>
+  <si>
+    <t>YES (Good)</t>
+  </si>
+  <si>
+    <t>YES (Poor)</t>
+  </si>
+  <si>
+    <t>Suburb, peaker plant</t>
+  </si>
+  <si>
+    <t>YES (Fixed residential)</t>
+  </si>
+  <si>
+    <t>YES (Fixed industrial)</t>
+  </si>
+  <si>
+    <t>YES (Wholesale, lower)</t>
+  </si>
+  <si>
+    <t>YES (Wholesale, higher)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -206,8 +270,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -238,6 +309,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -263,18 +339,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -288,6 +367,1364 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>885091</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>23447</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>52202</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>195486</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23C3813C-0E98-0C47-AFFE-A9AF5D17E796}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1740876" y="1817078"/>
+          <a:ext cx="286664" cy="371331"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" b="1"/>
+            <a:t>A</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>426359</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>192511</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>753693</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>165328</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD4C9DB4-374A-0276-13F2-D2319C6CB45C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2515135" y="2559193"/>
+          <a:ext cx="327334" cy="367264"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" b="1"/>
+            <a:t>B</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>617852</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>7266</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>110239</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>177306</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FF2CB75-6A39-9C12-43D6-670C76CF4217}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3448975" y="2398774"/>
+          <a:ext cx="348172" cy="369332"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" b="1"/>
+            <a:t>C</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>448442</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>135464</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>796614</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>106211</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22CDC21B-7037-9288-A49E-2AA6AD308BBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2423780" y="3523433"/>
+          <a:ext cx="348172" cy="369332"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" b="1"/>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>791938</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>148466</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>263487</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>119213</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3FB1801-CF0B-196B-207D-B6601ED976B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3623061" y="2938558"/>
+          <a:ext cx="327334" cy="369332"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" b="1"/>
+            <a:t>E</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>787262</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>118739</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>239576</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>89486</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D2F8237-035E-551D-21CC-5B9396DDA31F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4474170" y="4104585"/>
+          <a:ext cx="308098" cy="369332"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" b="1"/>
+            <a:t>F</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1087211</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>195486</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>426359</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>178919</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Straight Connector 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E78DA75-8E9B-AA06-4182-C9C8BE35939C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="3" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1938858" y="2167721"/>
+          <a:ext cx="576277" cy="575104"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>753693</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190898</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>617852</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>178919</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D7111EC-156C-A760-5072-13CCBFC466FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="4" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2842469" y="2557580"/>
+          <a:ext cx="715807" cy="185245"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>590026</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>165328</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>622528</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>135464</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Straight Connector 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{185CEBB1-C6E4-2082-119C-0E545E98A21D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="5" idx="0"/>
+          <a:endCxn id="3" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2678802" y="2926457"/>
+          <a:ext cx="32502" cy="561807"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>796614</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133839</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>791938</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>120837</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Straight Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3878C1BB-6F77-5684-15D3-20155EAD7EA7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="5" idx="3"/>
+          <a:endCxn id="6" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2771952" y="3123224"/>
+          <a:ext cx="851109" cy="584875"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>263487</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133839</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>787262</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>104113</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Straight Connector 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C41E678-7B66-113B-4CEB-B99FC87C1BA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="6" idx="3"/>
+          <a:endCxn id="7" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3950395" y="3123224"/>
+          <a:ext cx="523775" cy="1166027"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>796614</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>120837</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>787262</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>104113</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="Straight Connector 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07E43C34-F962-82EA-C622-6C857BB1A8D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="5" idx="3"/>
+          <a:endCxn id="7" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2771952" y="3708099"/>
+          <a:ext cx="1702218" cy="581152"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>753693</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>178919</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>791938</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133839</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4AC403E-3640-4F0A-A279-07744ABAC09C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="6" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2842469" y="2742825"/>
+          <a:ext cx="889893" cy="349367"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="lgDash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>789869</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>177306</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>791938</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133839</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="Straight Connector 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1BC7E60-1C52-498E-A1DB-26EC9EAA9264}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="6" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3730293" y="2741212"/>
+          <a:ext cx="2069" cy="350980"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="lgDash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1087211</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>195486</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>617852</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190898</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Straight Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A9DB867-AD51-456A-9972-5DC0918B3B32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="4" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1938858" y="2167721"/>
+          <a:ext cx="1619418" cy="389859"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="lgDash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -607,384 +2044,423 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773A3E98-2DE2-3246-BBBC-A7EFDC583254}">
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
+        <v>70</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
+        <v>69</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
+        <v>37</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" t="s">
-        <v>8</v>
+        <v>71</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H16" t="s">
         <v>42</v>
       </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D21" t="s">
-        <v>19</v>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H21" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4290B951-8F0C-5349-9F5D-132B582F7790}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9634E36E-1C52-4E1E-8DF9-F0779669CEEC}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.59765625" customWidth="1"/>
+    <col min="2" max="2" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7">
         <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -993,130 +2469,100 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2155F4B6-E3DC-3443-8726-D23849DFF292}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4290B951-8F0C-5349-9F5D-132B582F7790}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="B8" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1125,34 +2571,170 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88A2DE3-4377-5F45-9DB5-C20D6C029B92}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2155F4B6-E3DC-3443-8726-D23849DFF292}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88A2DE3-4377-5F45-9DB5-C20D6C029B92}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.3984375" customWidth="1"/>
+    <col min="3" max="3" width="19.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>41</v>
       </c>
       <c r="C2">
         <v>25</v>
@@ -1161,12 +2743,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -1175,12 +2757,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -1189,20 +2771,20 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>25</v>
@@ -1211,12 +2793,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -1225,12 +2807,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -1239,12 +2821,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>40</v>
@@ -1253,31 +2835,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>25</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11">
-        <v>25</v>
-      </c>
-      <c r="D11">
         <v>0.1</v>
       </c>
     </row>

--- a/Case_Study/Sample_use_case_setup.xlsx
+++ b/Case_Study/Sample_use_case_setup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jbrauch\Desktop\HYPSTAT open sourcing\HYPSTAT\Case_Study\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yli6/Desktop/NREL/Project/HYPSTAT/HYPSTAT_github/HYPSTAT/Case_Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6572167F-6DB3-4143-ADA7-C1D4743DA91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319E2148-11A5-854C-888C-1292BB0B942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8240C5C8-55BB-784E-92A0-705DB0403669}"/>
+    <workbookView xWindow="11980" yWindow="4400" windowWidth="23260" windowHeight="12580" xr2:uid="{8240C5C8-55BB-784E-92A0-705DB0403669}"/>
   </bookViews>
   <sheets>
     <sheet name="Zone" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="79">
   <si>
     <t>Node</t>
   </si>
@@ -256,6 +256,27 @@
   </si>
   <si>
     <t>YES (Wholesale, higher)</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Sample State</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Florida</t>
   </si>
 </sst>
 </file>
@@ -2044,15 +2065,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773A3E98-2DE2-3246-BBBC-A7EFDC583254}">
-  <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2089,8 +2110,11 @@
       <c r="L1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2127,8 +2151,11 @@
       <c r="L2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2165,8 +2192,11 @@
       <c r="L3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2203,8 +2233,11 @@
       <c r="L4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2241,8 +2274,11 @@
       <c r="L5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2279,8 +2315,11 @@
       <c r="L6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2317,33 +2356,36 @@
       <c r="L7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H18" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H20" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H21" t="s">
         <v>18</v>
       </c>
@@ -2357,15 +2399,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9634E36E-1C52-4E1E-8DF9-F0779669CEEC}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" customWidth="1"/>
-    <col min="2" max="2" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.8984375" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2379,7 +2421,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2393,7 +2435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2407,7 +2449,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2421,7 +2463,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2435,7 +2477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2449,7 +2491,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2471,13 +2513,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4290B951-8F0C-5349-9F5D-132B582F7790}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -2485,7 +2527,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -2493,7 +2535,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
@@ -2501,7 +2543,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -2509,7 +2551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -2517,7 +2559,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -2525,7 +2567,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
@@ -2533,7 +2575,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
@@ -2541,7 +2583,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -2549,7 +2591,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
@@ -2557,7 +2599,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
@@ -2573,13 +2615,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2155F4B6-E3DC-3443-8726-D23849DFF292}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -2590,7 +2632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -2601,7 +2643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2654,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -2623,7 +2665,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -2634,7 +2676,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -2645,7 +2687,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
@@ -2656,7 +2698,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
@@ -2667,7 +2709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -2678,7 +2720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
@@ -2689,7 +2731,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
@@ -2708,14 +2750,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88A2DE3-4377-5F45-9DB5-C20D6C029B92}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2729,7 +2771,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2743,7 +2785,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -2757,7 +2799,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2771,7 +2813,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -2779,7 +2821,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2793,7 +2835,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2807,7 +2849,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -2821,7 +2863,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2835,7 +2877,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>

--- a/Case_Study/Sample_use_case_setup.xlsx
+++ b/Case_Study/Sample_use_case_setup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yli6/Desktop/NREL/Project/HYPSTAT/HYPSTAT_github/HYPSTAT/Case_Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319E2148-11A5-854C-888C-1292BB0B942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EC4394-DF90-C74D-A29A-34D68012F741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11980" yWindow="4400" windowWidth="23260" windowHeight="12580" xr2:uid="{8240C5C8-55BB-784E-92A0-705DB0403669}"/>
   </bookViews>
@@ -299,7 +299,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,6 +335,12 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -364,7 +370,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -372,6 +378,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
@@ -2065,12 +2073,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773A3E98-2DE2-3246-BBBC-A7EFDC583254}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="8" max="8" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -2360,35 +2369,175 @@
         <v>78</v>
       </c>
     </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="7"/>
+    </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="7"/>
       <c r="H16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7"/>
       <c r="H17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="7"/>
       <c r="H18" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="7"/>
       <c r="H19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="7"/>
       <c r="H20" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="7"/>
       <c r="H21" t="s">
         <v>18</v>
       </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
